--- a/Weights&Centers.xlsx
+++ b/Weights&Centers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gshelton28\Documents\MATLAB\MBSE\ship-mbse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89882E7B-8E82-490E-B491-BAA1C511D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD60CF7-03DE-495F-A65C-C815DF60987B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="8595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -171,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -534,16 +535,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" customWidth="1"/>
-    <col min="2" max="2" width="15.3671875" customWidth="1"/>
-    <col min="3" max="3" width="24.62890625" customWidth="1"/>
-    <col min="4" max="4" width="16.05078125" customWidth="1"/>
-    <col min="5" max="5" width="18.47265625" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -560,7 +561,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5">
       <c r="B2" t="s">
         <v>43</v>
       </c>
@@ -574,601 +575,601 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:E3" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
         <f t="shared" ref="B4:E37" ca="1" si="1">RANDBETWEEN(1,100)</f>
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>1</v>
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="1"/>
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="1"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="1"/>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <f ca="1">RANDBETWEEN(1,100)</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <f t="shared" ca="1" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <f ca="1">RANDBETWEEN(1,100)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
         <v>65</v>
       </c>
       <c r="E10">
-        <f t="shared" ca="1" si="1"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <f ca="1">RANDBETWEEN(1,100)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E11">
-        <f t="shared" ca="1" si="1"/>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <f ca="1">RANDBETWEEN(1,100)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="1"/>
         <v>78</v>
       </c>
-      <c r="D13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
       <c r="E13">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="1"/>
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="1"/>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="1"/>
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="1"/>
@@ -1176,137 +1177,137 @@
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D35">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E35">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="1"/>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="D37">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
